--- a/jain/books.xlsx
+++ b/jain/books.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parth.shah\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\$MainSitePFin\jainlibrary\jain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B80D137-6DD5-48AE-ABFF-96FA884777D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9555CD7-A376-47E0-9680-89DED42DFB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,9 +492,6 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Jainam Jayati Shasanam - Chandrakant Lodaya</t>
-  </si>
-  <si>
     <t>EPUB/Jain Vigyan Part 1 to 6.epub</t>
   </si>
   <si>
@@ -528,7 +525,10 @@
     <t>Tattvartha</t>
   </si>
   <si>
-    <t>Gujarati/Jainam Jayati Shasanam - Chandrakant Lodaya/Tattvartha/Jain Vigyan Part 1 to 6/index.html</t>
+    <t>Chandrakant Lodaya(JJS)</t>
+  </si>
+  <si>
+    <t>Gujarati/Chandrakant Lodaya(JJS)/Tattvartha/Jain Vigyan Part 1 to 6/index.html</t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -937,7 +937,7 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -951,13 +951,13 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G2" t="str">
         <f>E2&amp;"/"&amp;D2&amp;"/"&amp;C2&amp;"/"&amp;B2&amp;"/"&amp;B2&amp;".html"</f>
@@ -986,13 +986,13 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" ref="G3:G42" si="0">E3&amp;"/"&amp;D3&amp;"/"&amp;C3&amp;"/"&amp;B3&amp;"/"&amp;B3&amp;".html"</f>
@@ -1021,13 +1021,13 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" si="0"/>
@@ -1056,13 +1056,13 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" si="0"/>
@@ -1091,13 +1091,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="0"/>
@@ -1126,13 +1126,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
@@ -1161,13 +1161,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" si="0"/>
@@ -1196,13 +1196,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="0"/>
@@ -1231,13 +1231,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" si="0"/>
@@ -1266,13 +1266,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" si="0"/>
@@ -1301,13 +1301,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" si="0"/>
@@ -1336,13 +1336,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="0"/>
@@ -1371,13 +1371,13 @@
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" si="0"/>
@@ -1406,13 +1406,13 @@
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" si="0"/>
@@ -1441,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" si="0"/>
@@ -1476,13 +1476,13 @@
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" si="0"/>
@@ -1511,13 +1511,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" si="0"/>
@@ -1546,13 +1546,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="0"/>
@@ -1581,13 +1581,13 @@
         <v>65</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" si="0"/>
@@ -1616,13 +1616,13 @@
         <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" si="0"/>
@@ -1651,13 +1651,13 @@
         <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="0"/>
@@ -1686,13 +1686,13 @@
         <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" si="0"/>
@@ -1721,13 +1721,13 @@
         <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" si="0"/>
@@ -1756,13 +1756,13 @@
         <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="0"/>
@@ -1791,13 +1791,13 @@
         <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" si="0"/>
@@ -1826,13 +1826,13 @@
         <v>65</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G27" t="str">
         <f t="shared" si="0"/>
@@ -1861,13 +1861,13 @@
         <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="0"/>
@@ -1896,13 +1896,13 @@
         <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G29" t="str">
         <f t="shared" si="0"/>
@@ -1931,13 +1931,13 @@
         <v>93</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="0"/>
@@ -1966,13 +1966,13 @@
         <v>93</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="0"/>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="0"/>
@@ -2036,13 +2036,13 @@
         <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="0"/>
@@ -2071,13 +2071,13 @@
         <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="0"/>
@@ -2106,13 +2106,13 @@
         <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G35" t="str">
         <f t="shared" si="0"/>
@@ -2141,13 +2141,13 @@
         <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G36" t="str">
         <f t="shared" si="0"/>
@@ -2185,7 +2185,7 @@
         <v>121</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H37" t="s">
         <v>122</v>
@@ -2219,7 +2219,7 @@
         <v>121</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H38" t="s">
         <v>125</v>
@@ -2238,7 +2238,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C39" t="s">
         <v>121</v>
@@ -2323,7 +2323,7 @@
         <v>135</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s">
         <v>136</v>
@@ -2345,10 +2345,10 @@
         <v>138</v>
       </c>
       <c r="C42" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" t="s">
         <v>151</v>
-      </c>
-      <c r="D42" t="s">
-        <v>140</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -2360,14 +2360,14 @@
         <v>152</v>
       </c>
       <c r="H42" t="s">
+        <v>140</v>
+      </c>
+      <c r="I42" t="s">
         <v>141</v>
       </c>
-      <c r="I42" t="s">
-        <v>142</v>
-      </c>
       <c r="J42" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Jainam Jayati Shasanam - Chandrakant Lodaya\Tattvartha\Jain Vigyan Part 1 to 6"</v>
+        <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Chandrakant Lodaya(JJS)\Tattvartha\Jain Vigyan Part 1 to 6"</v>
       </c>
     </row>
   </sheetData>

--- a/jain/books.xlsx
+++ b/jain/books.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\$MainSitePFin\jainlibrary\jain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9555CD7-A376-47E0-9680-89DED42DFB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646648AB-7160-4804-9B64-6D1D906F22C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="152">
   <si>
     <t>BookID</t>
   </si>
@@ -511,9 +511,6 @@
   </si>
   <si>
     <t>Gujarati/Buddisagar Suri/Explaination/Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo/index.html</t>
-  </si>
-  <si>
-    <t>Gujarati/Subodhiben Masalia/QnA/Prashnottar Ratnamala Part 1/index.html</t>
   </si>
   <si>
     <t>Gujarati/Subodhiben Masalia/QnA/Prashnottar Ratnamala Part 2/index.html</t>
@@ -995,7 +992,7 @@
         <v>143</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G42" si="0">E3&amp;"/"&amp;D3&amp;"/"&amp;C3&amp;"/"&amp;B3&amp;"/"&amp;B3&amp;".html"</f>
+        <f t="shared" ref="G3:G40" si="0">E3&amp;"/"&amp;D3&amp;"/"&amp;C3&amp;"/"&amp;B3&amp;"/"&amp;B3&amp;".html"</f>
         <v>Gujarati/Aagams/Aanga Aagam/1- Acharanga Sutra Part 2/1- Acharanga Sutra Part 2.html</v>
       </c>
       <c r="H3" t="s">
@@ -2184,8 +2181,9 @@
       <c r="F37" t="s">
         <v>121</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>147</v>
+      <c r="G37" t="str">
+        <f t="shared" si="0"/>
+        <v>Gujarati/Subodhiben Masalia/QnA/Prashnottar Ratnamala Part 1/Prashnottar Ratnamala Part 1.html</v>
       </c>
       <c r="H37" t="s">
         <v>122</v>
@@ -2219,7 +2217,7 @@
         <v>121</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H38" t="s">
         <v>125</v>
@@ -2238,7 +2236,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C39" t="s">
         <v>121</v>
@@ -2345,10 +2343,10 @@
         <v>138</v>
       </c>
       <c r="C42" t="s">
+        <v>149</v>
+      </c>
+      <c r="D42" t="s">
         <v>150</v>
-      </c>
-      <c r="D42" t="s">
-        <v>151</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -2357,7 +2355,7 @@
         <v>139</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H42" t="s">
         <v>140</v>

--- a/jain/books.xlsx
+++ b/jain/books.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\$MainSitePFin\jainlibrary\jain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646648AB-7160-4804-9B64-6D1D906F22C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2780BA96-533A-4D8E-8EA5-1C9E86CCF18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Books" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="149">
   <si>
     <t>BookID</t>
   </si>
@@ -510,12 +510,6 @@
     <t>Aagams</t>
   </si>
   <si>
-    <t>Gujarati/Buddisagar Suri/Explaination/Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo/index.html</t>
-  </si>
-  <si>
-    <t>Gujarati/Subodhiben Masalia/QnA/Prashnottar Ratnamala Part 2/index.html</t>
-  </si>
-  <si>
     <t>Prashnottar Ratnamala Part 3</t>
   </si>
   <si>
@@ -523,9 +517,6 @@
   </si>
   <si>
     <t>Chandrakant Lodaya(JJS)</t>
-  </si>
-  <si>
-    <t>Gujarati/Chandrakant Lodaya(JJS)/Tattvartha/Jain Vigyan Part 1 to 6/index.html</t>
   </si>
 </sst>
 </file>
@@ -992,7 +983,7 @@
         <v>143</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G40" si="0">E3&amp;"/"&amp;D3&amp;"/"&amp;C3&amp;"/"&amp;B3&amp;"/"&amp;B3&amp;".html"</f>
+        <f t="shared" ref="G3:G42" si="0">E3&amp;"/"&amp;D3&amp;"/"&amp;C3&amp;"/"&amp;B3&amp;"/"&amp;B3&amp;".html"</f>
         <v>Gujarati/Aagams/Aanga Aagam/1- Acharanga Sutra Part 2/1- Acharanga Sutra Part 2.html</v>
       </c>
       <c r="H3" t="s">
@@ -2216,8 +2207,9 @@
       <c r="F38" t="s">
         <v>121</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>147</v>
+      <c r="G38" t="str">
+        <f t="shared" si="0"/>
+        <v>Gujarati/Subodhiben Masalia/QnA/Prashnottar Ratnamala Part 2/Prashnottar Ratnamala Part 2.html</v>
       </c>
       <c r="H38" t="s">
         <v>125</v>
@@ -2236,7 +2228,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C39" t="s">
         <v>121</v>
@@ -2250,7 +2242,7 @@
       <c r="F39" t="s">
         <v>121</v>
       </c>
-      <c r="G39" s="1" t="str">
+      <c r="G39" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Subodhiben Masalia/QnA/Prashnottar Ratnamala Part 3/Prashnottar Ratnamala Part 3.html</v>
       </c>
@@ -2320,8 +2312,9 @@
       <c r="F41" t="s">
         <v>135</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>146</v>
+      <c r="G41" t="str">
+        <f t="shared" si="0"/>
+        <v>Gujarati/Buddisagar Suri/Explaination/Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo/Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo.html</v>
       </c>
       <c r="H41" t="s">
         <v>136</v>
@@ -2343,10 +2336,10 @@
         <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D42" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -2354,8 +2347,9 @@
       <c r="F42" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>151</v>
+      <c r="G42" t="str">
+        <f t="shared" si="0"/>
+        <v>Gujarati/Chandrakant Lodaya(JJS)/Tattvartha/Jain Vigyan Part 1 to 6/Jain Vigyan Part 1 to 6.html</v>
       </c>
       <c r="H42" t="s">
         <v>140</v>

--- a/jain/books.xlsx
+++ b/jain/books.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\$MainSitePFin\jainlibrary\jain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2780BA96-533A-4D8E-8EA5-1C9E86CCF18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5943BBC5-6F50-41A7-933D-2199A1CC6C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="74">
   <si>
     <t>BookID</t>
   </si>
@@ -105,327 +105,117 @@
     <t>Gujarati</t>
   </si>
   <si>
-    <t>EPUB/1-Acharanga Sutra Part 1.epub</t>
-  </si>
-  <si>
-    <t>PDF/1-Acharanga Sutra Part 1.pdf</t>
-  </si>
-  <si>
     <t>1- Acharanga Sutra Part 2</t>
   </si>
   <si>
-    <t>EPUB/1- Acharanga Sutra Part 2.epub</t>
-  </si>
-  <si>
-    <t>PDF/1- Acharanga Sutra Part 2.pdf</t>
-  </si>
-  <si>
     <t>2- Suyagadanga Sutra Part 1</t>
   </si>
   <si>
-    <t>EPUB/2- Suyagadanga Sutra Part 1.epub</t>
-  </si>
-  <si>
-    <t>PDF/2- Suyagadanga Sutra Part 1.pdf</t>
-  </si>
-  <si>
     <t>2 - Suyagadanga Sutra Part 2</t>
   </si>
   <si>
-    <t>EPUB/2 - Suyagadanga Sutra Part 2.epub</t>
-  </si>
-  <si>
-    <t>PDF/2 - Suyagadanga Sutra Part 2.pdf</t>
-  </si>
-  <si>
     <t>3 - Thananga Sutra Part 1</t>
   </si>
   <si>
-    <t>EPUB/3 - Thananga Sutra Part 1.epub</t>
-  </si>
-  <si>
-    <t>PDF/3 - Thananga Sutra Part 1.pdf</t>
-  </si>
-  <si>
     <t>3 - Thananga Sutra Part 2</t>
   </si>
   <si>
-    <t>EPUB/3 - Thananga Sutra Part 2.epub</t>
-  </si>
-  <si>
-    <t>PDF/3 - Thananga Sutra Part 2.pdf</t>
-  </si>
-  <si>
     <t>4 - Samvayanga Sutra</t>
   </si>
   <si>
-    <t>EPUB/4 - Samvayanga Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/4 - Samvayanga Sutra.pdf</t>
-  </si>
-  <si>
     <t>5 - Bhagavati Sutra Part 1</t>
   </si>
   <si>
-    <t>EPUB/5 - Bhagavati Sutra Part 1.epub</t>
-  </si>
-  <si>
-    <t>PDF/5 - Bhagavati Sutra Part 1.pdf</t>
-  </si>
-  <si>
     <t>5 - Bhagavati Sutra Part 2</t>
   </si>
   <si>
-    <t>EPUB/5 - Bhagavati Sutra Part 2.epub</t>
-  </si>
-  <si>
-    <t>PDF/5 - Bhagavati Sutra Part 2.pdf</t>
-  </si>
-  <si>
     <t>5 - Bhagavati Sutra Part 3</t>
   </si>
   <si>
-    <t>EPUB/5 - Bhagavati Sutra Part 3.epub</t>
-  </si>
-  <si>
-    <t>PDF/5 - Bhagavati Sutra Part 3.pdf</t>
-  </si>
-  <si>
     <t>5 - Bhagavati Sutra Part 4</t>
   </si>
   <si>
-    <t>EPUB/5 - Bhagavati Sutra Part 4.epub</t>
-  </si>
-  <si>
-    <t>PDF/5 - Bhagavati Sutra Part 4.pdf</t>
-  </si>
-  <si>
     <t>5 - Bhagavati Sutra Part 5</t>
   </si>
   <si>
-    <t>EPUB/5 - Bhagavati Sutra Part 5.epub</t>
-  </si>
-  <si>
-    <t>PDF/5 - Bhagavati Sutra Part 5.pdf</t>
-  </si>
-  <si>
     <t>6 - Gnatadharmakatha Sutra</t>
   </si>
   <si>
-    <t>EPUB/6 - Gnatadharmakatha Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/6 - Gnatadharmakatha Sutra.pdf</t>
-  </si>
-  <si>
     <t>7 - Upasakadashanga Sutra</t>
   </si>
   <si>
-    <t>EPUB/7 - Upasakadashanga Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/7 - Upasakadashanga Sutra.pdf</t>
-  </si>
-  <si>
     <t>8 - Antagada Sutra</t>
   </si>
   <si>
-    <t>EPUB/8 - Antagada Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/8 - Antagada Sutra.pdf</t>
-  </si>
-  <si>
     <t>9 - Anuttarovavai Sutra</t>
   </si>
   <si>
-    <t>EPUB/9 - Anuttarovavai Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/9 - Anuttarovavai Sutra.pdf</t>
-  </si>
-  <si>
     <t>10 - Prashnavyakaran Sutra</t>
   </si>
   <si>
-    <t>EPUB/10 - Prashnavyakaran Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/10 - Prashnavyakaran Sutra.pdf</t>
-  </si>
-  <si>
     <t>11 - Vipaka Sutra</t>
   </si>
   <si>
-    <t>EPUB/11 - Vipaka Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/11 - Vipaka Sutra.pdf</t>
-  </si>
-  <si>
     <t>1 - Uvvavai Sutra</t>
   </si>
   <si>
     <t>Upang Aagam</t>
   </si>
   <si>
-    <t>EPUB/1 - Uvvavai Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/1 - Uvvavai Sutra.pdf</t>
-  </si>
-  <si>
     <t>2 - Raipaseniya Sutra</t>
   </si>
   <si>
-    <t>EPUB/2 - Raipaseniya Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/2 - Raipaseniya Sutra.pdf</t>
-  </si>
-  <si>
     <t>3- JeevaJeevabhigam Sutra</t>
   </si>
   <si>
-    <t>EPUB/3- JeevaJeevabhigam Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/3- JeevaJeevabhigam Sutra.pdf</t>
-  </si>
-  <si>
     <t>4- Pannavanna Sutra Part 1</t>
   </si>
   <si>
-    <t>EPUB/4- Pannavanna Sutra Part 1.epub</t>
-  </si>
-  <si>
-    <t>PDF/4- Pannavanna Sutra Part 1.pdf</t>
-  </si>
-  <si>
     <t>4- Pannavanna Sutra Part 2</t>
   </si>
   <si>
-    <t>EPUB/4- Pannavanna Sutra Part 2.epub</t>
-  </si>
-  <si>
-    <t>PDF/4- Pannavanna Sutra Part 2.pdf</t>
-  </si>
-  <si>
     <t>4- Pannavanna Sutra Part 3</t>
   </si>
   <si>
-    <t>EPUB/4- Pannavanna Sutra Part 3.epub</t>
-  </si>
-  <si>
-    <t>PDF/4- Pannavanna Sutra Part 3.pdf</t>
-  </si>
-  <si>
     <t>5- Jambudhvip Sutra</t>
   </si>
   <si>
-    <t>EPUB/5- Jambudhvip Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/5- Jambudhvip Sutra.pdf</t>
-  </si>
-  <si>
     <t>6- Surya Pragnapti, 7- Chandra Pragnapti Sutra</t>
   </si>
   <si>
-    <t>EPUB/6- Surya Pragnapti, 7- Chandra Pragnapti Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/6- Surya Pragnapti, 7- Chandra Pragnapti Sutra.pdf</t>
-  </si>
-  <si>
     <t>8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra</t>
   </si>
   <si>
-    <t>EPUB/8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra.pdf</t>
-  </si>
-  <si>
     <t>1- Utaradhyayan Sutra Part 1</t>
   </si>
   <si>
     <t>Mool Sutras</t>
   </si>
   <si>
-    <t>EPUB/1- Utaradhyayan Sutra Part 1.epub</t>
-  </si>
-  <si>
-    <t>PDF/1- Utaradhyayan Sutra Part 1.pdf</t>
-  </si>
-  <si>
     <t>1- Utaradhyayan Sutra Part 2</t>
   </si>
   <si>
-    <t>EPUB/1- Utaradhyayan Sutra Part 2.epub</t>
-  </si>
-  <si>
-    <t>PDF/1- Utaradhyayan Sutra Part 2.pdf</t>
-  </si>
-  <si>
     <t>2 - Dasvaikalika Sutra</t>
   </si>
   <si>
-    <t>EPUB/2 - Dasvaikalika Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/2 - Dasvaikalika Sutra.pdf</t>
-  </si>
-  <si>
     <t>3- Nandi Sutra</t>
   </si>
   <si>
-    <t>EPUB/3- Nandi Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/3- Nandi Sutra.pdf</t>
-  </si>
-  <si>
     <t>4- Anuyogdwar Sutra</t>
   </si>
   <si>
-    <t>EPUB/4- Anuyogdwar Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/4- Anuyogdwar Sutra.pdf</t>
-  </si>
-  <si>
     <t>1- Nishith Sutra</t>
   </si>
   <si>
     <t>Chhed Sutras</t>
   </si>
   <si>
-    <t>EPUB/1- Nishith Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/1- Nishith Sutra.pdf</t>
-  </si>
-  <si>
     <t>2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra</t>
   </si>
   <si>
-    <t>EPUB/2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra.pdf</t>
-  </si>
-  <si>
     <t>Aavasyaka Sutra</t>
   </si>
   <si>
-    <t>EPUB/Aavasyaka Sutra.epub</t>
-  </si>
-  <si>
-    <t>PDF/Aavasyaka Sutra.pdf</t>
-  </si>
-  <si>
     <t>Prashnottar Ratnamala Part 1</t>
   </si>
   <si>
@@ -438,21 +228,9 @@
     <t>QnA</t>
   </si>
   <si>
-    <t>EPUB/Prashnottar Ratnamala Part 1.epub</t>
-  </si>
-  <si>
-    <t>PDF/Prashnottar Ratnamala Part 1.pdf</t>
-  </si>
-  <si>
     <t>Prashnottar Ratnamala Part 2</t>
   </si>
   <si>
-    <t>EPUB/Prashnottar Ratnamala Part 2.epub</t>
-  </si>
-  <si>
-    <t>PDF/Prashnottar Ratnamala Part 2.pdf</t>
-  </si>
-  <si>
     <t>Atmanusasana - Precept on the Soul</t>
   </si>
   <si>
@@ -465,12 +243,6 @@
     <t>Self Discipline</t>
   </si>
   <si>
-    <t>EPUB/Atmanusasana - Precept on the Soul.epub</t>
-  </si>
-  <si>
-    <t>PDF/Atmanusasana - Precept on the Soul.pdf</t>
-  </si>
-  <si>
     <t>Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo</t>
   </si>
   <si>
@@ -480,24 +252,12 @@
     <t>Comparative Study</t>
   </si>
   <si>
-    <t>EPUB/Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo.epub</t>
-  </si>
-  <si>
-    <t>PDF/Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo.pdf</t>
-  </si>
-  <si>
     <t>Jain Vigyan Part 1 to 6</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>EPUB/Jain Vigyan Part 1 to 6.epub</t>
-  </si>
-  <si>
-    <t>PDF/Jain Vigyan Part 1 to 6.pdf</t>
-  </si>
-  <si>
     <t>Tags</t>
   </si>
   <si>
@@ -517,6 +277,21 @@
   </si>
   <si>
     <t>Chandrakant Lodaya(JJS)</t>
+  </si>
+  <si>
+    <t>Bhaktaamar Saartha</t>
+  </si>
+  <si>
+    <t>Sutra</t>
+  </si>
+  <si>
+    <t>Mantungasuri</t>
+  </si>
+  <si>
+    <t>Sanskrit</t>
+  </si>
+  <si>
+    <t>Bhaktamar</t>
   </si>
 </sst>
 </file>
@@ -882,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -913,7 +688,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -925,7 +700,7 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -939,23 +714,25 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G2" t="str">
         <f>E2&amp;"/"&amp;D2&amp;"/"&amp;C2&amp;"/"&amp;B2&amp;"/"&amp;B2&amp;".html"</f>
         <v>Gujarati/Aagams/Aanga Aagam/1-Acharanga Sutra Part 1/1-Acharanga Sutra Part 1.html</v>
       </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
+      <c r="H2" t="str">
+        <f>"EPUB/"&amp;B2&amp;".epub"</f>
+        <v>EPUB/1-Acharanga Sutra Part 1.epub</v>
+      </c>
+      <c r="I2" t="str">
+        <f>"PDF/"&amp;B2&amp;".pdf"</f>
+        <v>PDF/1-Acharanga Sutra Part 1.pdf</v>
       </c>
       <c r="J2" s="1" t="str">
         <f>"md "&amp;""""&amp;"D:\$MainSitePFin\jainlibrary\jain\"&amp;E2&amp;"\"&amp;D2&amp;"\"&amp;C2&amp;"\"&amp;B2&amp;""""</f>
@@ -968,1398 +745,1514 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G42" si="0">E3&amp;"/"&amp;D3&amp;"/"&amp;C3&amp;"/"&amp;B3&amp;"/"&amp;B3&amp;".html"</f>
+        <f t="shared" ref="G3:G43" si="0">E3&amp;"/"&amp;D3&amp;"/"&amp;C3&amp;"/"&amp;B3&amp;"/"&amp;B3&amp;".html"</f>
         <v>Gujarati/Aagams/Aanga Aagam/1- Acharanga Sutra Part 2/1- Acharanga Sutra Part 2.html</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H43" si="1">"EPUB/"&amp;B3&amp;".epub"</f>
+        <v>EPUB/1- Acharanga Sutra Part 2.epub</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I43" si="2">"PDF/"&amp;B3&amp;".pdf"</f>
+        <v>PDF/1- Acharanga Sutra Part 2.pdf</v>
       </c>
       <c r="J3" s="1" t="str">
-        <f t="shared" ref="J3:J42" si="1">"md "&amp;""""&amp;"D:\$MainSitePFin\jainlibrary\jain\"&amp;E3&amp;"\"&amp;D3&amp;"\"&amp;C3&amp;"\"&amp;B3&amp;""""</f>
+        <f t="shared" ref="J3:J43" si="3">"md "&amp;""""&amp;"D:\$MainSitePFin\jainlibrary\jain\"&amp;E3&amp;"\"&amp;D3&amp;"\"&amp;C3&amp;"\"&amp;B3&amp;""""</f>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\1- Acharanga Sutra Part 2"</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <f t="shared" ref="A4:A42" si="2">+A3+1</f>
+        <f t="shared" ref="A4:A42" si="4">+A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/2- Suyagadanga Sutra Part 1/2- Suyagadanga Sutra Part 1.html</v>
       </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" t="s">
-        <v>18</v>
+      <c r="H4" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/2- Suyagadanga Sutra Part 1.epub</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/2- Suyagadanga Sutra Part 1.pdf</v>
       </c>
       <c r="J4" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\2- Suyagadanga Sutra Part 1"</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/2 - Suyagadanga Sutra Part 2/2 - Suyagadanga Sutra Part 2.html</v>
       </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
+      <c r="H5" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/2 - Suyagadanga Sutra Part 2.epub</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/2 - Suyagadanga Sutra Part 2.pdf</v>
       </c>
       <c r="J5" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\2 - Suyagadanga Sutra Part 2"</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/3 - Thananga Sutra Part 1/3 - Thananga Sutra Part 1.html</v>
       </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" t="s">
-        <v>24</v>
+      <c r="H6" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/3 - Thananga Sutra Part 1.epub</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/3 - Thananga Sutra Part 1.pdf</v>
       </c>
       <c r="J6" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\3 - Thananga Sutra Part 1"</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/3 - Thananga Sutra Part 2/3 - Thananga Sutra Part 2.html</v>
       </c>
-      <c r="H7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" t="s">
-        <v>27</v>
+      <c r="H7" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/3 - Thananga Sutra Part 2.epub</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/3 - Thananga Sutra Part 2.pdf</v>
       </c>
       <c r="J7" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\3 - Thananga Sutra Part 2"</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/4 - Samvayanga Sutra/4 - Samvayanga Sutra.html</v>
       </c>
-      <c r="H8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" t="s">
-        <v>30</v>
+      <c r="H8" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/4 - Samvayanga Sutra.epub</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/4 - Samvayanga Sutra.pdf</v>
       </c>
       <c r="J8" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\4 - Samvayanga Sutra"</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/5 - Bhagavati Sutra Part 1/5 - Bhagavati Sutra Part 1.html</v>
       </c>
-      <c r="H9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" t="s">
-        <v>33</v>
+      <c r="H9" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/5 - Bhagavati Sutra Part 1.epub</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/5 - Bhagavati Sutra Part 1.pdf</v>
       </c>
       <c r="J9" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 1"</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/5 - Bhagavati Sutra Part 2/5 - Bhagavati Sutra Part 2.html</v>
       </c>
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" t="s">
-        <v>36</v>
+      <c r="H10" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/5 - Bhagavati Sutra Part 2.epub</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/5 - Bhagavati Sutra Part 2.pdf</v>
       </c>
       <c r="J10" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 2"</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/5 - Bhagavati Sutra Part 3/5 - Bhagavati Sutra Part 3.html</v>
       </c>
-      <c r="H11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" t="s">
-        <v>39</v>
+      <c r="H11" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/5 - Bhagavati Sutra Part 3.epub</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/5 - Bhagavati Sutra Part 3.pdf</v>
       </c>
       <c r="J11" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 3"</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/5 - Bhagavati Sutra Part 4/5 - Bhagavati Sutra Part 4.html</v>
       </c>
-      <c r="H12" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" t="s">
-        <v>42</v>
+      <c r="H12" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/5 - Bhagavati Sutra Part 4.epub</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/5 - Bhagavati Sutra Part 4.pdf</v>
       </c>
       <c r="J12" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 4"</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/5 - Bhagavati Sutra Part 5/5 - Bhagavati Sutra Part 5.html</v>
       </c>
-      <c r="H13" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" t="s">
-        <v>45</v>
+      <c r="H13" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/5 - Bhagavati Sutra Part 5.epub</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/5 - Bhagavati Sutra Part 5.pdf</v>
       </c>
       <c r="J13" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 5"</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/6 - Gnatadharmakatha Sutra/6 - Gnatadharmakatha Sutra.html</v>
       </c>
-      <c r="H14" t="s">
-        <v>47</v>
-      </c>
-      <c r="I14" t="s">
-        <v>48</v>
+      <c r="H14" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/6 - Gnatadharmakatha Sutra.epub</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/6 - Gnatadharmakatha Sutra.pdf</v>
       </c>
       <c r="J14" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\6 - Gnatadharmakatha Sutra"</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/7 - Upasakadashanga Sutra/7 - Upasakadashanga Sutra.html</v>
       </c>
-      <c r="H15" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" t="s">
-        <v>51</v>
+      <c r="H15" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/7 - Upasakadashanga Sutra.epub</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/7 - Upasakadashanga Sutra.pdf</v>
       </c>
       <c r="J15" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\7 - Upasakadashanga Sutra"</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/8 - Antagada Sutra/8 - Antagada Sutra.html</v>
       </c>
-      <c r="H16" t="s">
-        <v>53</v>
-      </c>
-      <c r="I16" t="s">
-        <v>54</v>
+      <c r="H16" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/8 - Antagada Sutra.epub</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/8 - Antagada Sutra.pdf</v>
       </c>
       <c r="J16" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\8 - Antagada Sutra"</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/9 - Anuttarovavai Sutra/9 - Anuttarovavai Sutra.html</v>
       </c>
-      <c r="H17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" t="s">
-        <v>57</v>
+      <c r="H17" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/9 - Anuttarovavai Sutra.epub</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/9 - Anuttarovavai Sutra.pdf</v>
       </c>
       <c r="J17" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\9 - Anuttarovavai Sutra"</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/10 - Prashnavyakaran Sutra/10 - Prashnavyakaran Sutra.html</v>
       </c>
-      <c r="H18" t="s">
-        <v>59</v>
-      </c>
-      <c r="I18" t="s">
-        <v>60</v>
+      <c r="H18" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/10 - Prashnavyakaran Sutra.epub</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/10 - Prashnavyakaran Sutra.pdf</v>
       </c>
       <c r="J18" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\10 - Prashnavyakaran Sutra"</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Aanga Aagam/11 - Vipaka Sutra/11 - Vipaka Sutra.html</v>
       </c>
-      <c r="H19" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" t="s">
-        <v>63</v>
+      <c r="H19" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/11 - Vipaka Sutra.epub</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/11 - Vipaka Sutra.pdf</v>
       </c>
       <c r="J19" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\11 - Vipaka Sutra"</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Upang Aagam/1 - Uvvavai Sutra/1 - Uvvavai Sutra.html</v>
       </c>
-      <c r="H20" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" t="s">
-        <v>67</v>
+      <c r="H20" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/1 - Uvvavai Sutra.epub</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/1 - Uvvavai Sutra.pdf</v>
       </c>
       <c r="J20" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\1 - Uvvavai Sutra"</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Upang Aagam/2 - Raipaseniya Sutra/2 - Raipaseniya Sutra.html</v>
       </c>
-      <c r="H21" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" t="s">
-        <v>70</v>
+      <c r="H21" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/2 - Raipaseniya Sutra.epub</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/2 - Raipaseniya Sutra.pdf</v>
       </c>
       <c r="J21" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\2 - Raipaseniya Sutra"</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Upang Aagam/3- JeevaJeevabhigam Sutra/3- JeevaJeevabhigam Sutra.html</v>
       </c>
-      <c r="H22" t="s">
-        <v>72</v>
-      </c>
-      <c r="I22" t="s">
-        <v>73</v>
+      <c r="H22" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/3- JeevaJeevabhigam Sutra.epub</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/3- JeevaJeevabhigam Sutra.pdf</v>
       </c>
       <c r="J22" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\3- JeevaJeevabhigam Sutra"</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Upang Aagam/4- Pannavanna Sutra Part 1/4- Pannavanna Sutra Part 1.html</v>
       </c>
-      <c r="H23" t="s">
-        <v>75</v>
-      </c>
-      <c r="I23" t="s">
-        <v>76</v>
+      <c r="H23" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/4- Pannavanna Sutra Part 1.epub</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/4- Pannavanna Sutra Part 1.pdf</v>
       </c>
       <c r="J23" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\4- Pannavanna Sutra Part 1"</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Upang Aagam/4- Pannavanna Sutra Part 2/4- Pannavanna Sutra Part 2.html</v>
       </c>
-      <c r="H24" t="s">
-        <v>78</v>
-      </c>
-      <c r="I24" t="s">
-        <v>79</v>
+      <c r="H24" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/4- Pannavanna Sutra Part 2.epub</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/4- Pannavanna Sutra Part 2.pdf</v>
       </c>
       <c r="J24" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\4- Pannavanna Sutra Part 2"</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Upang Aagam/4- Pannavanna Sutra Part 3/4- Pannavanna Sutra Part 3.html</v>
       </c>
-      <c r="H25" t="s">
-        <v>81</v>
-      </c>
-      <c r="I25" t="s">
-        <v>82</v>
+      <c r="H25" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/4- Pannavanna Sutra Part 3.epub</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/4- Pannavanna Sutra Part 3.pdf</v>
       </c>
       <c r="J25" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\4- Pannavanna Sutra Part 3"</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Upang Aagam/5- Jambudhvip Sutra/5- Jambudhvip Sutra.html</v>
       </c>
-      <c r="H26" t="s">
-        <v>84</v>
-      </c>
-      <c r="I26" t="s">
-        <v>85</v>
+      <c r="H26" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/5- Jambudhvip Sutra.epub</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/5- Jambudhvip Sutra.pdf</v>
       </c>
       <c r="J26" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\5- Jambudhvip Sutra"</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G27" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Upang Aagam/6- Surya Pragnapti, 7- Chandra Pragnapti Sutra/6- Surya Pragnapti, 7- Chandra Pragnapti Sutra.html</v>
       </c>
-      <c r="H27" t="s">
-        <v>87</v>
-      </c>
-      <c r="I27" t="s">
-        <v>88</v>
+      <c r="H27" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/6- Surya Pragnapti, 7- Chandra Pragnapti Sutra.epub</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/6- Surya Pragnapti, 7- Chandra Pragnapti Sutra.pdf</v>
       </c>
       <c r="J27" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\6- Surya Pragnapti, 7- Chandra Pragnapti Sutra"</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Upang Aagam/8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra/8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra.html</v>
       </c>
-      <c r="H28" t="s">
-        <v>90</v>
-      </c>
-      <c r="I28" t="s">
-        <v>91</v>
+      <c r="H28" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra.epub</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra.pdf</v>
       </c>
       <c r="J28" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra"</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G29" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Mool Sutras/1- Utaradhyayan Sutra Part 1/1- Utaradhyayan Sutra Part 1.html</v>
       </c>
-      <c r="H29" t="s">
-        <v>94</v>
-      </c>
-      <c r="I29" t="s">
-        <v>95</v>
+      <c r="H29" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/1- Utaradhyayan Sutra Part 1.epub</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/1- Utaradhyayan Sutra Part 1.pdf</v>
       </c>
       <c r="J29" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\1- Utaradhyayan Sutra Part 1"</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Mool Sutras/1- Utaradhyayan Sutra Part 2/1- Utaradhyayan Sutra Part 2.html</v>
       </c>
-      <c r="H30" t="s">
-        <v>97</v>
-      </c>
-      <c r="I30" t="s">
-        <v>98</v>
+      <c r="H30" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/1- Utaradhyayan Sutra Part 2.epub</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/1- Utaradhyayan Sutra Part 2.pdf</v>
       </c>
       <c r="J30" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\1- Utaradhyayan Sutra Part 2"</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Mool Sutras/2 - Dasvaikalika Sutra/2 - Dasvaikalika Sutra.html</v>
       </c>
-      <c r="H31" t="s">
-        <v>100</v>
-      </c>
-      <c r="I31" t="s">
-        <v>101</v>
+      <c r="H31" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/2 - Dasvaikalika Sutra.epub</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/2 - Dasvaikalika Sutra.pdf</v>
       </c>
       <c r="J31" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\2 - Dasvaikalika Sutra"</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Mool Sutras/3- Nandi Sutra/3- Nandi Sutra.html</v>
       </c>
-      <c r="H32" t="s">
-        <v>103</v>
-      </c>
-      <c r="I32" t="s">
-        <v>104</v>
+      <c r="H32" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/3- Nandi Sutra.epub</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/3- Nandi Sutra.pdf</v>
       </c>
       <c r="J32" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\3- Nandi Sutra"</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Mool Sutras/4- Anuyogdwar Sutra/4- Anuyogdwar Sutra.html</v>
       </c>
-      <c r="H33" t="s">
-        <v>106</v>
-      </c>
-      <c r="I33" t="s">
-        <v>107</v>
+      <c r="H33" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/4- Anuyogdwar Sutra.epub</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/4- Anuyogdwar Sutra.pdf</v>
       </c>
       <c r="J33" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\4- Anuyogdwar Sutra"</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Chhed Sutras/1- Nishith Sutra/1- Nishith Sutra.html</v>
       </c>
-      <c r="H34" t="s">
-        <v>110</v>
-      </c>
-      <c r="I34" t="s">
-        <v>111</v>
+      <c r="H34" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/1- Nishith Sutra.epub</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/1- Nishith Sutra.pdf</v>
       </c>
       <c r="J34" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Chhed Sutras\1- Nishith Sutra"</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G35" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Chhed Sutras/2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra/2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra.html</v>
       </c>
-      <c r="H35" t="s">
-        <v>113</v>
-      </c>
-      <c r="I35" t="s">
-        <v>114</v>
+      <c r="H35" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra.epub</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra.pdf</v>
       </c>
       <c r="J35" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Chhed Sutras\2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra"</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="G36" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Aagams/Chhed Sutras/Aavasyaka Sutra/Aavasyaka Sutra.html</v>
       </c>
-      <c r="H36" t="s">
-        <v>116</v>
-      </c>
-      <c r="I36" t="s">
-        <v>117</v>
+      <c r="H36" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/Aavasyaka Sutra.epub</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/Aavasyaka Sutra.pdf</v>
       </c>
       <c r="J36" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Chhed Sutras\Aavasyaka Sutra"</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Subodhiben Masalia/QnA/Prashnottar Ratnamala Part 1/Prashnottar Ratnamala Part 1.html</v>
       </c>
-      <c r="H37" t="s">
-        <v>122</v>
-      </c>
-      <c r="I37" t="s">
-        <v>123</v>
+      <c r="H37" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/Prashnottar Ratnamala Part 1.epub</v>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/Prashnottar Ratnamala Part 1.pdf</v>
       </c>
       <c r="J37" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 1"</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="G38" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Subodhiben Masalia/QnA/Prashnottar Ratnamala Part 2/Prashnottar Ratnamala Part 2.html</v>
       </c>
-      <c r="H38" t="s">
-        <v>125</v>
-      </c>
-      <c r="I38" t="s">
-        <v>126</v>
+      <c r="H38" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/Prashnottar Ratnamala Part 2.epub</v>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/Prashnottar Ratnamala Part 2.pdf</v>
       </c>
       <c r="J38" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 2"</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Subodhiben Masalia/QnA/Prashnottar Ratnamala Part 3/Prashnottar Ratnamala Part 3.html</v>
       </c>
-      <c r="H39" t="s">
-        <v>125</v>
-      </c>
-      <c r="I39" t="s">
-        <v>126</v>
+      <c r="H39" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/Prashnottar Ratnamala Part 3.epub</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/Prashnottar Ratnamala Part 3.pdf</v>
       </c>
       <c r="J39" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 3"</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="E40" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="F40" t="s">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="G40" t="str">
         <f t="shared" si="0"/>
         <v>English/Vijay K Jain/Explaination/Atmanusasana - Precept on the Soul/Atmanusasana - Precept on the Soul.html</v>
       </c>
-      <c r="H40" t="s">
-        <v>131</v>
-      </c>
-      <c r="I40" t="s">
-        <v>132</v>
+      <c r="H40" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/Atmanusasana - Precept on the Soul.epub</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/Atmanusasana - Precept on the Soul.pdf</v>
       </c>
       <c r="J40" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\English\Vijay K Jain\Explaination\Atmanusasana - Precept on the Soul"</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="G41" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Buddisagar Suri/Explaination/Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo/Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo.html</v>
       </c>
-      <c r="H41" t="s">
-        <v>136</v>
-      </c>
-      <c r="I41" t="s">
-        <v>137</v>
+      <c r="H41" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo.epub</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo.pdf</v>
       </c>
       <c r="J41" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Buddisagar Suri\Explaination\Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo"</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>147</v>
+        <v>67</v>
       </c>
       <c r="D42" t="s">
-        <v>148</v>
+        <v>68</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="G42" t="str">
         <f t="shared" si="0"/>
         <v>Gujarati/Chandrakant Lodaya(JJS)/Tattvartha/Jain Vigyan Part 1 to 6/Jain Vigyan Part 1 to 6.html</v>
       </c>
-      <c r="H42" t="s">
-        <v>140</v>
-      </c>
-      <c r="I42" t="s">
-        <v>141</v>
+      <c r="H42" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/Jain Vigyan Part 1 to 6.epub</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/Jain Vigyan Part 1 to 6.pdf</v>
       </c>
       <c r="J42" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Chandrakant Lodaya(JJS)\Tattvartha\Jain Vigyan Part 1 to 6"</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" t="s">
+        <v>73</v>
+      </c>
+      <c r="G43" t="str">
+        <f t="shared" si="0"/>
+        <v>Sanskrit/Mantungasuri/Sutra/Bhaktaamar Saartha/Bhaktaamar Saartha.html</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="1"/>
+        <v>EPUB/Bhaktaamar Saartha.epub</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="2"/>
+        <v>PDF/Bhaktaamar Saartha.pdf</v>
+      </c>
+      <c r="J43" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>md "D:\$MainSitePFin\jainlibrary\jain\Sanskrit\Mantungasuri\Sutra\Bhaktaamar Saartha"</v>
       </c>
     </row>
   </sheetData>

--- a/jain/books.xlsx
+++ b/jain/books.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\$MainSitePFin\jainlibrary\jain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5943BBC5-6F50-41A7-933D-2199A1CC6C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A066E69-9C58-46B2-AF8F-29D15B77A9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1065" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Books" sheetId="1" r:id="rId1"/>
@@ -65,12 +65,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{D07E86AE-8AD9-4AA3-A640-72575E5AEBFE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>PARTH DEEPAKKUMAR SHAH:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Put this file names in HTML_FILES = [ in html2epub3.py</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="82">
   <si>
     <t>BookID</t>
   </si>
@@ -292,6 +316,30 @@
   </si>
   <si>
     <t>Bhaktamar</t>
+  </si>
+  <si>
+    <t>"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\1-Acharanga Sutra Part 1\1-Acharanga Sutra Part 1.html"</t>
+  </si>
+  <si>
+    <t>"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\1- Acharanga Sutra Part 2\1- Acharanga Sutra Part 2.html"</t>
+  </si>
+  <si>
+    <t>"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 1\Prashnottar Ratnamala Part 1.html"</t>
+  </si>
+  <si>
+    <t>"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 2\Prashnottar Ratnamala Part 2.html"</t>
+  </si>
+  <si>
+    <t>"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 3\Prashnottar Ratnamala Part 3.html"</t>
+  </si>
+  <si>
+    <t>"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Buddisagar Suri\Explaination\Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo\Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo.html"</t>
+  </si>
+  <si>
+    <t>"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Chandrakant Lodaya(JJS)\Tattvartha\Jain Vigyan Part 1 to 6\Jain Vigyan Part 1 to 6.html"</t>
+  </si>
+  <si>
+    <t>for epub generation</t>
   </si>
 </sst>
 </file>
@@ -657,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -671,7 +719,7 @@
     <col min="10" max="10" width="46.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -702,8 +750,11 @@
       <c r="J1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -738,8 +789,12 @@
         <f>"md "&amp;""""&amp;"D:\$MainSitePFin\jainlibrary\jain\"&amp;E2&amp;"\"&amp;D2&amp;"\"&amp;C2&amp;"\"&amp;B2&amp;""""</f>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\1-Acharanga Sutra Part 1"</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" t="str">
+        <f>"r"&amp;""""&amp;"D:\$MainSitePFin\jainlibrary\jain\"&amp;E2&amp;"\"&amp;D2&amp;"\"&amp;C2&amp;"\"&amp;B2&amp;"\"&amp;B2&amp;".html"&amp;""""&amp;","</f>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\1-Acharanga Sutra Part 1\1-Acharanga Sutra Part 1.html",</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>+A2+1</f>
         <v>2</v>
@@ -775,10 +830,14 @@
         <f t="shared" ref="J3:J43" si="3">"md "&amp;""""&amp;"D:\$MainSitePFin\jainlibrary\jain\"&amp;E3&amp;"\"&amp;D3&amp;"\"&amp;C3&amp;"\"&amp;B3&amp;""""</f>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\1- Acharanga Sutra Part 2"</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K43" si="4">"r"&amp;""""&amp;"D:\$MainSitePFin\jainlibrary\jain\"&amp;E3&amp;"\"&amp;D3&amp;"\"&amp;C3&amp;"\"&amp;B3&amp;"\"&amp;B3&amp;".html"&amp;""""&amp;","</f>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\1- Acharanga Sutra Part 2\1- Acharanga Sutra Part 2.html",</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
-        <f t="shared" ref="A4:A42" si="4">+A3+1</f>
+        <f t="shared" ref="A4:A42" si="5">+A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -812,10 +871,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\2- Suyagadanga Sutra Part 1"</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\2- Suyagadanga Sutra Part 1\2- Suyagadanga Sutra Part 1.html",</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -849,10 +912,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\2 - Suyagadanga Sutra Part 2"</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\2 - Suyagadanga Sutra Part 2\2 - Suyagadanga Sutra Part 2.html",</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -886,10 +953,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\3 - Thananga Sutra Part 1"</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\3 - Thananga Sutra Part 1\3 - Thananga Sutra Part 1.html",</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -923,10 +994,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\3 - Thananga Sutra Part 2"</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\3 - Thananga Sutra Part 2\3 - Thananga Sutra Part 2.html",</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -960,10 +1035,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\4 - Samvayanga Sutra"</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\4 - Samvayanga Sutra\4 - Samvayanga Sutra.html",</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -997,10 +1076,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 1"</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 1\5 - Bhagavati Sutra Part 1.html",</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -1034,10 +1117,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 2"</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 2\5 - Bhagavati Sutra Part 2.html",</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -1071,10 +1158,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 3"</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 3\5 - Bhagavati Sutra Part 3.html",</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -1108,10 +1199,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 4"</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 4\5 - Bhagavati Sutra Part 4.html",</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="B13" t="s">
@@ -1145,10 +1240,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 5"</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\5 - Bhagavati Sutra Part 5\5 - Bhagavati Sutra Part 5.html",</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="B14" t="s">
@@ -1182,10 +1281,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\6 - Gnatadharmakatha Sutra"</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\6 - Gnatadharmakatha Sutra\6 - Gnatadharmakatha Sutra.html",</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="B15" t="s">
@@ -1219,10 +1322,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\7 - Upasakadashanga Sutra"</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\7 - Upasakadashanga Sutra\7 - Upasakadashanga Sutra.html",</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="B16" t="s">
@@ -1256,10 +1363,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\8 - Antagada Sutra"</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\8 - Antagada Sutra\8 - Antagada Sutra.html",</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="B17" t="s">
@@ -1293,10 +1404,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\9 - Anuttarovavai Sutra"</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\9 - Anuttarovavai Sutra\9 - Anuttarovavai Sutra.html",</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="B18" t="s">
@@ -1330,10 +1445,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\10 - Prashnavyakaran Sutra"</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\10 - Prashnavyakaran Sutra\10 - Prashnavyakaran Sutra.html",</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="B19" t="s">
@@ -1367,10 +1486,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\11 - Vipaka Sutra"</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\11 - Vipaka Sutra\11 - Vipaka Sutra.html",</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="B20" t="s">
@@ -1404,10 +1527,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\1 - Uvvavai Sutra"</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\1 - Uvvavai Sutra\1 - Uvvavai Sutra.html",</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="B21" t="s">
@@ -1441,10 +1568,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\2 - Raipaseniya Sutra"</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\2 - Raipaseniya Sutra\2 - Raipaseniya Sutra.html",</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="B22" t="s">
@@ -1478,10 +1609,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\3- JeevaJeevabhigam Sutra"</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\3- JeevaJeevabhigam Sutra\3- JeevaJeevabhigam Sutra.html",</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="B23" t="s">
@@ -1515,10 +1650,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\4- Pannavanna Sutra Part 1"</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\4- Pannavanna Sutra Part 1\4- Pannavanna Sutra Part 1.html",</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="B24" t="s">
@@ -1552,10 +1691,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\4- Pannavanna Sutra Part 2"</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K24" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\4- Pannavanna Sutra Part 2\4- Pannavanna Sutra Part 2.html",</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="B25" t="s">
@@ -1589,10 +1732,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\4- Pannavanna Sutra Part 3"</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K25" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\4- Pannavanna Sutra Part 3\4- Pannavanna Sutra Part 3.html",</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="B26" t="s">
@@ -1626,10 +1773,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\5- Jambudhvip Sutra"</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\5- Jambudhvip Sutra\5- Jambudhvip Sutra.html",</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="B27" t="s">
@@ -1663,10 +1814,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\6- Surya Pragnapti, 7- Chandra Pragnapti Sutra"</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\6- Surya Pragnapti, 7- Chandra Pragnapti Sutra\6- Surya Pragnapti, 7- Chandra Pragnapti Sutra.html",</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="B28" t="s">
@@ -1700,10 +1855,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra"</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Upang Aagam\8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra\8- Niryavalika, 9- Kalpavatansika, 10- Pushpika, 11- Pushpachulika, 12- Vrasnidasah Sutra.html",</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="B29" t="s">
@@ -1737,10 +1896,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\1- Utaradhyayan Sutra Part 1"</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\1- Utaradhyayan Sutra Part 1\1- Utaradhyayan Sutra Part 1.html",</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="B30" t="s">
@@ -1774,10 +1937,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\1- Utaradhyayan Sutra Part 2"</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\1- Utaradhyayan Sutra Part 2\1- Utaradhyayan Sutra Part 2.html",</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="B31" t="s">
@@ -1811,10 +1978,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\2 - Dasvaikalika Sutra"</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\2 - Dasvaikalika Sutra\2 - Dasvaikalika Sutra.html",</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
       <c r="B32" t="s">
@@ -1848,10 +2019,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\3- Nandi Sutra"</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\3- Nandi Sutra\3- Nandi Sutra.html",</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
       <c r="B33" t="s">
@@ -1885,10 +2060,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\4- Anuyogdwar Sutra"</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Mool Sutras\4- Anuyogdwar Sutra\4- Anuyogdwar Sutra.html",</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>33</v>
       </c>
       <c r="B34" t="s">
@@ -1922,10 +2101,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Chhed Sutras\1- Nishith Sutra"</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Chhed Sutras\1- Nishith Sutra\1- Nishith Sutra.html",</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -1959,10 +2142,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Chhed Sutras\2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra"</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K35" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Chhed Sutras\2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra\2- Dashashrut, 3- Bruhatkalpa, 4- Vyavahar Sutra.html",</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -1996,10 +2183,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Chhed Sutras\Aavasyaka Sutra"</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K36" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Chhed Sutras\Aavasyaka Sutra\Aavasyaka Sutra.html",</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -2033,10 +2224,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 1"</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K37" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 1\Prashnottar Ratnamala Part 1.html",</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -2070,10 +2265,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 2"</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K38" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 2\Prashnottar Ratnamala Part 2.html",</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -2107,10 +2306,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 3"</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K39" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 3\Prashnottar Ratnamala Part 3.html",</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
       <c r="B40" t="s">
@@ -2144,10 +2347,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\English\Vijay K Jain\Explaination\Atmanusasana - Precept on the Soul"</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K40" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\English\Vijay K Jain\Explaination\Atmanusasana - Precept on the Soul\Atmanusasana - Precept on the Soul.html",</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="B41" t="s">
@@ -2181,10 +2388,14 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Buddisagar Suri\Explaination\Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo"</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K41" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Buddisagar Suri\Explaination\Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo\Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo.html",</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>41</v>
       </c>
       <c r="B42" t="s">
@@ -2218,8 +2429,12 @@
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Gujarati\Chandrakant Lodaya(JJS)\Tattvartha\Jain Vigyan Part 1 to 6"</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K42" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Chandrakant Lodaya(JJS)\Tattvartha\Jain Vigyan Part 1 to 6\Jain Vigyan Part 1 to 6.html",</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2253,12 +2468,80 @@
       <c r="J43" s="1" t="str">
         <f t="shared" si="3"/>
         <v>md "D:\$MainSitePFin\jainlibrary\jain\Sanskrit\Mantungasuri\Sutra\Bhaktaamar Saartha"</v>
+      </c>
+      <c r="K43" t="str">
+        <f t="shared" si="4"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Sanskrit\Mantungasuri\Sutra\Bhaktaamar Saartha\Bhaktaamar Saartha.html",</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K47" t="s">
+        <v>74</v>
+      </c>
+      <c r="L47" t="str">
+        <f>"r"&amp;K47&amp;","</f>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\1-Acharanga Sutra Part 1\1-Acharanga Sutra Part 1.html",</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K48" t="s">
+        <v>75</v>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" ref="L48:L53" si="6">"r"&amp;K48&amp;","</f>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Aagams\Aanga Aagam\1- Acharanga Sutra Part 2\1- Acharanga Sutra Part 2.html",</v>
+      </c>
+    </row>
+    <row r="49" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>76</v>
+      </c>
+      <c r="L49" t="str">
+        <f t="shared" si="6"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 1\Prashnottar Ratnamala Part 1.html",</v>
+      </c>
+    </row>
+    <row r="50" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K50" t="s">
+        <v>77</v>
+      </c>
+      <c r="L50" t="str">
+        <f t="shared" si="6"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 2\Prashnottar Ratnamala Part 2.html",</v>
+      </c>
+    </row>
+    <row r="51" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
+        <v>78</v>
+      </c>
+      <c r="L51" t="str">
+        <f t="shared" si="6"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Subodhiben Masalia\QnA\Prashnottar Ratnamala Part 3\Prashnottar Ratnamala Part 3.html",</v>
+      </c>
+    </row>
+    <row r="52" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>79</v>
+      </c>
+      <c r="L52" t="str">
+        <f t="shared" si="6"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Buddisagar Suri\Explaination\Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo\Jain Christian Samvad - Jain Dharma ane khristi dharma no mukablo.html",</v>
+      </c>
+    </row>
+    <row r="53" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K53" t="s">
+        <v>80</v>
+      </c>
+      <c r="L53" t="str">
+        <f t="shared" si="6"/>
+        <v>r"D:\$MainSitePFin\jainlibrary\jain\Gujarati\Chandrakant Lodaya(JJS)\Tattvartha\Jain Vigyan Part 1 to 6\Jain Vigyan Part 1 to 6.html",</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I42" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>